--- a/JP (Exclude Game)/Dialog/Drama/fiama.xlsx
+++ b/JP (Exclude Game)/Dialog/Drama/fiama.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="164">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -382,20 +382,16 @@
     <t xml:space="preserve">firstDream</t>
   </si>
   <si>
-    <t xml:space="preserve">私の夢を見た？</t>
+    <t xml:space="preserve">n/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">giveStoryBook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あら、#pc_name#。</t>
   </si>
   <si>
     <t xml:space="preserve">I wish you would die.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…そう、よほどひどく頭を打ったのね。まずはしっかり休養をとるためにもベッドを作ってみたらどう？
-眠い時に「瞑想」を行うことでも睡眠はとれるけど、ベッドを使えばいつでも休むことができるし、疲労回復の効果も高いのよ。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">giveStoryBook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">あら、#pc_name#。</t>
   </si>
   <si>
     <t xml:space="preserve">そう、まだ奇妙な夢を見ているのね。
@@ -1704,15 +1700,18 @@
         <v>110</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H92" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="I92" s="4" t="s">
-        <v>112</v>
+      <c r="I92" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1722,7 +1721,7 @@
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1730,10 +1729,10 @@
         <v>29</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1741,7 +1740,7 @@
         <v>30</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1751,7 +1750,7 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1759,10 +1758,10 @@
         <v>31</v>
       </c>
       <c r="I102" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="J102" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="J102" s="4" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1770,18 +1769,18 @@
         <v>33</v>
       </c>
       <c r="I103" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="J103" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="J103" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D104" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1791,7 +1790,7 @@
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1799,15 +1798,15 @@
         <v>32</v>
       </c>
       <c r="I109" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J109" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="J109" s="4" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D111" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1817,15 +1816,15 @@
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D116" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1834,10 +1833,10 @@
         <v>34</v>
       </c>
       <c r="I117" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="J117" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="J117" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1845,10 +1844,10 @@
         <v>35</v>
       </c>
       <c r="I118" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="J118" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="J118" s="4" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1856,15 +1855,15 @@
         <v>36</v>
       </c>
       <c r="I119" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="J119" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="J119" s="4" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D120" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1874,7 +1873,7 @@
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1886,18 +1885,18 @@
         <v>37</v>
       </c>
       <c r="I126" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J126" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="J126" s="4" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D127" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1907,7 +1906,7 @@
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,10 +1918,10 @@
         <v>38</v>
       </c>
       <c r="I132" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="J132" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="J132" s="4" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1930,15 +1929,15 @@
         <v>39</v>
       </c>
       <c r="I133" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="J133" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="J133" s="4" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D134" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1948,15 +1947,15 @@
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D142" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1964,10 +1963,10 @@
         <v>41</v>
       </c>
       <c r="I145" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="J145" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="J145" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1975,15 +1974,15 @@
         <v>42</v>
       </c>
       <c r="I146" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="J146" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="J146" s="4" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>26</v>
@@ -1992,15 +1991,15 @@
         <v>43</v>
       </c>
       <c r="I147" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J147" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="J147" s="4" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>26</v>
@@ -2009,15 +2008,15 @@
         <v>44</v>
       </c>
       <c r="I148" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="J148" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="J148" s="4" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>26</v>
@@ -2026,15 +2025,15 @@
         <v>45</v>
       </c>
       <c r="I149" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J149" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="J149" s="4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>26</v>
@@ -2044,15 +2043,15 @@
         <v>46</v>
       </c>
       <c r="I150" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J150" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="J150" s="4" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>26</v>
@@ -2061,15 +2060,15 @@
         <v>47</v>
       </c>
       <c r="I151" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="J151" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="J151" s="4" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>26</v>
@@ -2078,10 +2077,10 @@
         <v>48</v>
       </c>
       <c r="I152" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="J152" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="J152" s="4" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2090,7 +2089,7 @@
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I154" s="4"/>
     </row>
@@ -2102,10 +2101,10 @@
         <v>49</v>
       </c>
       <c r="I156" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J156" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="J156" s="4" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2113,12 +2112,12 @@
         <v>57</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D158" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
